--- a/Mobile/Settings/assets/Noti Categories.xlsx
+++ b/Mobile/Settings/assets/Noti Categories.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CorpID\notification\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E80DADC9-0F51-4F58-9C69-09B3A15766B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EAA59B7-068B-4D7F-9413-AD03B9F49E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-33000" yWindow="-10060" windowWidth="31520" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-31410" yWindow="-9040" windowWidth="29740" windowHeight="17570" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="185">
   <si>
     <t>Onboarding</t>
   </si>
@@ -486,6 +487,139 @@
     <t>RP / AR / Admin no action after 30 day RP update identified from Doc index search.
 System suspended the RP after WIPI identified existing RP no longer registered as RP in CR</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Scheduled System Maintenance Notice</t>
+  </si>
+  <si>
+    <t>Password Changed</t>
+  </si>
+  <si>
+    <t>Mobile Changed</t>
+  </si>
+  <si>
+    <t>Email Changed</t>
+  </si>
+  <si>
+    <t>Device Bound</t>
+  </si>
+  <si>
+    <t>Device Unbound</t>
+  </si>
+  <si>
+    <t>User Invited</t>
+  </si>
+  <si>
+    <t>User Joined</t>
+  </si>
+  <si>
+    <t>User Removed</t>
+  </si>
+  <si>
+    <t>Admin Appointed</t>
+  </si>
+  <si>
+    <t>Admin Removed</t>
+  </si>
+  <si>
+    <t>RP Appointed</t>
+  </si>
+  <si>
+    <t>RP Removed</t>
+  </si>
+  <si>
+    <t>AR Appointed</t>
+  </si>
+  <si>
+    <t>AR Removed</t>
+  </si>
+  <si>
+    <t>Authorisation Granted</t>
+  </si>
+  <si>
+    <t>Authorisation Revoked</t>
+  </si>
+  <si>
+    <t>Delegation Created</t>
+  </si>
+  <si>
+    <t>Delegation Expired</t>
+  </si>
+  <si>
+    <t>Certificate Application</t>
+  </si>
+  <si>
+    <t>Certificate Approval</t>
+  </si>
+  <si>
+    <t>Certificate Issued</t>
+  </si>
+  <si>
+    <t>Certificate Expiry</t>
+  </si>
+  <si>
+    <t>Certificate Revoked</t>
+  </si>
+  <si>
+    <t>Certificate Renewed</t>
+  </si>
+  <si>
+    <t>CorpID Registration Submitted</t>
+  </si>
+  <si>
+    <t>Registration Approved</t>
+  </si>
+  <si>
+    <t>Registration Rejected</t>
+  </si>
+  <si>
+    <t>Registration Suspended</t>
+  </si>
+  <si>
+    <t>Suspicious Login</t>
+  </si>
+  <si>
+    <t>Account Locked</t>
+  </si>
+  <si>
+    <t>Account Suspended</t>
+  </si>
+  <si>
+    <t>Application Submitted</t>
+  </si>
+  <si>
+    <t>Approval Pending</t>
+  </si>
+  <si>
+    <t>Approval Completed</t>
+  </si>
+  <si>
+    <t>Request Rejected</t>
+  </si>
+  <si>
+    <t>Company Membership</t>
+  </si>
+  <si>
+    <t>Personal Account</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Authorisation / Delegation</t>
+  </si>
+  <si>
+    <t>Certificate Lifecycle</t>
+  </si>
+  <si>
+    <t>Registration Lifecycle</t>
+  </si>
+  <si>
+    <t>Security Events</t>
+  </si>
+  <si>
+    <t>Application Workflow</t>
+  </si>
+  <si>
+    <t>Boardcast Announcement</t>
   </si>
 </sst>
 </file>
@@ -1572,4 +1706,239 @@
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="85" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AA96C5F-B002-47EB-95DA-742022D5CE5C}">
+  <dimension ref="A1:B51"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="24.85546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B14" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B47" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>